--- a/main/ig/FRConditionLMCDAFHIR.xlsx
+++ b/main/ig/FRConditionLMCDAFHIR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="75">
   <si>
     <t>Property</t>
   </si>
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T15:39:37+00:00</t>
+    <t>2026-08-05T12:15:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -79,7 +79,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Mapping des éléments du modèle métier FRLMProbleme vers le profil CDA FRCDAProbleme, puis vers le profil FHIR FRConditionDocument.</t>
+    <t>Mapping des éléments du modèle métier FRLMCondition vers le profil CDA FRCDAProbleme, puis vers le profil FHIR FRConditionDocument.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -100,7 +100,7 @@
     <t>Target</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-probleme</t>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-condition</t>
   </si>
   <si>
     <t/>
@@ -109,7 +109,7 @@
     <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-cda-probleme</t>
   </si>
   <si>
-    <t>FRLMProbleme</t>
+    <t>FRLMCondition</t>
   </si>
   <si>
     <t>equivalent</t>
@@ -118,91 +118,73 @@
     <t>FRCDAProbleme</t>
   </si>
   <si>
-    <t>FRLMProbleme.identifiant</t>
+    <t>FRLMCondition.header.identifier</t>
   </si>
   <si>
     <t>FRCDAProbleme.id</t>
   </si>
   <si>
-    <t>FRLMProbleme.type</t>
+    <t>FRLMCondition.type</t>
   </si>
   <si>
     <t>FRCDAProbleme.code</t>
   </si>
   <si>
-    <t>FRLMProbleme.description</t>
-  </si>
-  <si>
-    <t>FRCDAProbleme.text</t>
-  </si>
-  <si>
-    <t>FRLMProbleme.problemeObserve</t>
+    <t>FRLMCondition.problem</t>
   </si>
   <si>
     <t>FRCDAProbleme.value</t>
   </si>
   <si>
-    <t>FRLMProbleme.statut</t>
-  </si>
-  <si>
-    <t>FRCDAProbleme.statusCode</t>
-  </si>
-  <si>
-    <t>FRLMProbleme.dateDebutProbleme</t>
+    <t>FRLMCondition.period</t>
+  </si>
+  <si>
+    <t>FRCDAProbleme.effectiveTime</t>
+  </si>
+  <si>
+    <t>FRLMCondition.period.onsetDate</t>
   </si>
   <si>
     <t>FRCDAProbleme.effectiveTime.low</t>
   </si>
   <si>
-    <t>FRLMProbleme.dateFinProbleme</t>
+    <t>FRLMCondition.period.endDate</t>
   </si>
   <si>
     <t>FRCDAProbleme.effectiveTime.high</t>
   </si>
   <si>
-    <t>FRLMProbleme.statutProbleme</t>
+    <t>FRLMCondition.header.status</t>
   </si>
   <si>
     <t>FRCDAProbleme.entryRelationship:frStatutDuProbleme</t>
   </si>
   <si>
-    <t>FRLMProbleme.severite</t>
+    <t>FRLMCondition.severity</t>
   </si>
   <si>
     <t>FRCDAProbleme.entryRelationship:frSeverite</t>
   </si>
   <si>
-    <t>FRLMProbleme.certitude</t>
+    <t>FRLMCondition.diagnosisAssertionStatus</t>
   </si>
   <si>
     <t>FRCDAProbleme.entryRelationship:frCertitude</t>
   </si>
   <si>
-    <t>FRLMProbleme.statutClinique</t>
+    <t>FRLMCondition.clinicalStatus</t>
   </si>
   <si>
     <t>FRCDAProbleme.entryRelationship:frStatutCliniqueDuPatient</t>
   </si>
   <si>
-    <t>FRLMProbleme.reference</t>
-  </si>
-  <si>
-    <t>FRCDAProbleme.reference</t>
-  </si>
-  <si>
-    <t>FRLMProbleme.reference.externalDocument.identifiant</t>
-  </si>
-  <si>
-    <t>FRCDAProbleme.reference.externalDocument.id</t>
-  </si>
-  <si>
-    <t>FRLMProbleme.reference.externalDocument.text.reference</t>
+    <t>FRLMCondition.reference</t>
   </si>
   <si>
     <t>FRCDAProbleme.reference.externalDocument.text.reference</t>
   </si>
   <si>
-    <t>FRLMProbleme.commentaire</t>
+    <t>FRLMCondition.note</t>
   </si>
   <si>
     <t>FRCDAProbleme.entryRelationship:frCommentaireER</t>
@@ -220,15 +202,15 @@
     <t>FRConditionDocument.category</t>
   </si>
   <si>
-    <t>FRConditionDocument.category.text</t>
-  </si>
-  <si>
     <t>FRConditionDocument.code</t>
   </si>
   <si>
     <t>FRConditionDocument.clinicalStatus</t>
   </si>
   <si>
+    <t>related-to</t>
+  </si>
+  <si>
     <t>FRConditionDocument.onsetDateTime</t>
   </si>
   <si>
@@ -244,10 +226,13 @@
     <t>FRConditionDocument.stage.summary</t>
   </si>
   <si>
-    <t>FRConditionDocument.evidence.detail</t>
-  </si>
-  <si>
-    <t>FRConditionDocument.evidence.detail:FRDocumentReferenceDocument.identifier</t>
+    <t>FRLMCondition.bodySite</t>
+  </si>
+  <si>
+    <t>FRConditionDocument.bodySite</t>
+  </si>
+  <si>
+    <t>FRLMCondition.stage</t>
   </si>
   <si>
     <t>FRConditionDocument.evidence.detail:FRDocumentReferenceDocument.content.attachment.url</t>
@@ -505,7 +490,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -710,45 +695,6 @@
         <v>57</v>
       </c>
       <c r="E15" s="2"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="s" s="2">
-        <v>58</v>
-      </c>
-      <c r="B16" s="2"/>
-      <c r="C16" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D16" t="s" s="2">
-        <v>59</v>
-      </c>
-      <c r="E16" s="2"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="s" s="2">
-        <v>60</v>
-      </c>
-      <c r="B17" s="2"/>
-      <c r="C17" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D17" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="E17" s="2"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="s" s="2">
-        <v>62</v>
-      </c>
-      <c r="B18" s="2"/>
-      <c r="C18" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D18" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="E18" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -757,7 +703,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -779,7 +725,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>29</v>
@@ -788,7 +734,7 @@
         <v>29</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="E2" t="s" s="2">
         <v>29</v>
@@ -796,211 +742,196 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D8" t="s" s="2">
-        <v>70</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="D8" s="2"/>
       <c r="E8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="E10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D12" t="s" s="2">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D13" t="s" s="2">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="E13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D14" t="s" s="2">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="E14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D15" t="s" s="2">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="E15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D16" t="s" s="2">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="E16" s="2"/>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D17" t="s" s="2">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E17" s="2"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="B18" s="2"/>
-      <c r="C18" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D18" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E18" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/main/ig/FRConditionLMCDAFHIR.xlsx
+++ b/main/ig/FRConditionLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T12:15:23+00:00</t>
+    <t>2026-08-11T08:03:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRConditionLMCDAFHIR.xlsx
+++ b/main/ig/FRConditionLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T08:03:55+00:00</t>
+    <t>2026-08-11T09:29:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRConditionLMCDAFHIR.xlsx
+++ b/main/ig/FRConditionLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T09:29:09+00:00</t>
+    <t>2026-08-13T09:45:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRConditionLMCDAFHIR.xlsx
+++ b/main/ig/FRConditionLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T09:45:33+00:00</t>
+    <t>2026-08-13T14:36:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRConditionLMCDAFHIR.xlsx
+++ b/main/ig/FRConditionLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T14:36:19+00:00</t>
+    <t>2026-08-14T12:00:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRConditionLMCDAFHIR.xlsx
+++ b/main/ig/FRConditionLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T12:00:06+00:00</t>
+    <t>2026-08-14T14:57:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRConditionLMCDAFHIR.xlsx
+++ b/main/ig/FRConditionLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T14:57:39+00:00</t>
+    <t>2026-08-20T08:45:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -100,13 +100,13 @@
     <t>Target</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-condition</t>
+    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/fr-lm-condition|0.1.0</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-cda-probleme</t>
+    <t>https://interop.esante.gouv.fr/ig/cda/document-core/StructureDefinition/fr-cda-probleme|0.1.0</t>
   </si>
   <si>
     <t>FRLMCondition</t>
@@ -190,7 +190,7 @@
     <t>FRCDAProbleme.entryRelationship:frCommentaireER</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-condition-document</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-condition-document|0.1.0</t>
   </si>
   <si>
     <t>FRConditionDocument</t>

--- a/main/ig/FRConditionLMCDAFHIR.xlsx
+++ b/main/ig/FRConditionLMCDAFHIR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="78">
   <si>
     <t>Property</t>
   </si>
@@ -37,6 +37,9 @@
     <t>Name</t>
   </si>
   <si>
+    <t>FRConditionLMCDAFHIR</t>
+  </si>
+  <si>
     <t>Title</t>
   </si>
   <si>
@@ -52,10 +55,13 @@
     <t>Experimental</t>
   </si>
   <si>
+    <t>false</t>
+  </si>
+  <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T08:45:34+00:00</t>
+    <t>2026-08-31T15:12:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -100,7 +106,7 @@
     <t>Target</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/fr-lm-condition|0.1.0</t>
+    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMCondition|0.1.0</t>
   </si>
   <si>
     <t/>
@@ -115,130 +121,133 @@
     <t>equivalent</t>
   </si>
   <si>
+    <t>Observation</t>
+  </si>
+  <si>
     <t>FRCDAProbleme</t>
   </si>
   <si>
     <t>FRLMCondition.header.identifier</t>
   </si>
   <si>
-    <t>FRCDAProbleme.id</t>
+    <t>Observation.id</t>
   </si>
   <si>
     <t>FRLMCondition.type</t>
   </si>
   <si>
-    <t>FRCDAProbleme.code</t>
+    <t>Observation.code</t>
   </si>
   <si>
     <t>FRLMCondition.problem</t>
   </si>
   <si>
-    <t>FRCDAProbleme.value</t>
+    <t>Observation.value</t>
   </si>
   <si>
     <t>FRLMCondition.period</t>
   </si>
   <si>
-    <t>FRCDAProbleme.effectiveTime</t>
+    <t>Observation.effectiveTime</t>
   </si>
   <si>
     <t>FRLMCondition.period.onsetDate</t>
   </si>
   <si>
-    <t>FRCDAProbleme.effectiveTime.low</t>
+    <t>source-is-narrower-than-target</t>
   </si>
   <si>
     <t>FRLMCondition.period.endDate</t>
   </si>
   <si>
-    <t>FRCDAProbleme.effectiveTime.high</t>
-  </si>
-  <si>
     <t>FRLMCondition.header.status</t>
   </si>
   <si>
-    <t>FRCDAProbleme.entryRelationship:frStatutDuProbleme</t>
+    <t>Observation.entryRelationship:frStatutDuProbleme</t>
   </si>
   <si>
     <t>FRLMCondition.severity</t>
   </si>
   <si>
-    <t>FRCDAProbleme.entryRelationship:frSeverite</t>
+    <t>Observation.entryRelationship:frSeverite</t>
   </si>
   <si>
     <t>FRLMCondition.diagnosisAssertionStatus</t>
   </si>
   <si>
-    <t>FRCDAProbleme.entryRelationship:frCertitude</t>
+    <t>Observation.entryRelationship:frCertitude</t>
   </si>
   <si>
     <t>FRLMCondition.clinicalStatus</t>
   </si>
   <si>
-    <t>FRCDAProbleme.entryRelationship:frStatutCliniqueDuPatient</t>
+    <t>Observation.entryRelationship:frStatutCliniqueDuPatient</t>
   </si>
   <si>
     <t>FRLMCondition.reference</t>
   </si>
   <si>
-    <t>FRCDAProbleme.reference.externalDocument.text.reference</t>
+    <t>Observation.reference.externalDocument.text.reference</t>
   </si>
   <si>
     <t>FRLMCondition.note</t>
   </si>
   <si>
-    <t>FRCDAProbleme.entryRelationship:frCommentaireER</t>
+    <t>Observation.entryRelationship:frCommentaireER</t>
   </si>
   <si>
     <t>https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-condition-document|0.1.0</t>
   </si>
   <si>
+    <t>Condition</t>
+  </si>
+  <si>
     <t>FRConditionDocument</t>
   </si>
   <si>
-    <t>FRConditionDocument.identifier</t>
-  </si>
-  <si>
-    <t>FRConditionDocument.category</t>
-  </si>
-  <si>
-    <t>FRConditionDocument.code</t>
-  </si>
-  <si>
-    <t>FRConditionDocument.clinicalStatus</t>
+    <t>Condition.identifier</t>
+  </si>
+  <si>
+    <t>Condition.category</t>
+  </si>
+  <si>
+    <t>Condition.code</t>
+  </si>
+  <si>
+    <t>Condition.clinicalStatus</t>
   </si>
   <si>
     <t>related-to</t>
   </si>
   <si>
-    <t>FRConditionDocument.onsetDateTime</t>
-  </si>
-  <si>
-    <t>FRConditionDocument.abatementDateTime</t>
-  </si>
-  <si>
-    <t>FRConditionDocument.severity</t>
-  </si>
-  <si>
-    <t>FRConditionDocument.verificationStatus</t>
-  </si>
-  <si>
-    <t>FRConditionDocument.stage.summary</t>
+    <t>Condition.onset[x]:onsetDateTime</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementDateTime</t>
+  </si>
+  <si>
+    <t>Condition.severity</t>
+  </si>
+  <si>
+    <t>Condition.verificationStatus</t>
+  </si>
+  <si>
+    <t>Condition.stage.summary</t>
   </si>
   <si>
     <t>FRLMCondition.bodySite</t>
   </si>
   <si>
-    <t>FRConditionDocument.bodySite</t>
+    <t>Condition.bodySite</t>
   </si>
   <si>
     <t>FRLMCondition.stage</t>
   </si>
   <si>
-    <t>FRConditionDocument.evidence.detail:FRDocumentReferenceDocument.content.attachment.url</t>
-  </si>
-  <si>
-    <t>FRConditionDocument.note</t>
+    <t>Condition.evidence.detail</t>
+  </si>
+  <si>
+    <t>Condition.note</t>
   </si>
 </sst>
 </file>
@@ -407,79 +416,83 @@
       <c r="A4" t="s" s="2">
         <v>6</v>
       </c>
-      <c r="B4" s="2"/>
+      <c r="B4" t="s" s="2">
+        <v>7</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>11</v>
-      </c>
-      <c r="B7" s="2"/>
+        <v>12</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>13</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B14" s="2"/>
     </row>
@@ -495,204 +508,206 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D1" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="E1" t="s" s="1">
         <v>27</v>
-      </c>
-      <c r="E1" t="s" s="1">
-        <v>25</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E2" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="E3" s="2"/>
+        <v>35</v>
+      </c>
+      <c r="E3" t="s" s="2">
+        <v>36</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D12" t="s" s="2">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D13" t="s" s="2">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D14" t="s" s="2">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D15" t="s" s="2">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E15" s="2"/>
     </row>
@@ -708,228 +723,230 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D1" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="E1" t="s" s="1">
         <v>27</v>
-      </c>
-      <c r="E1" t="s" s="1">
-        <v>25</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E2" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>59</v>
-      </c>
-      <c r="E3" s="2"/>
+        <v>61</v>
+      </c>
+      <c r="E3" t="s" s="2">
+        <v>62</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D12" t="s" s="2">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D13" t="s" s="2">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="E13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D14" t="s" s="2">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="E14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D15" t="s" s="2">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="E15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D16" t="s" s="2">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="E16" s="2"/>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D17" t="s" s="2">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="E17" s="2"/>
     </row>

--- a/main/ig/FRConditionLMCDAFHIR.xlsx
+++ b/main/ig/FRConditionLMCDAFHIR.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T15:12:23+00:00</t>
+    <t>2026-09-04T14:19:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
